--- a/Documentation/DocRenew_Jira_Task_Sheet.xlsx
+++ b/Documentation/DocRenew_Jira_Task_Sheet.xlsx
@@ -1309,7 +1309,7 @@
         <v>39</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>1</v>
@@ -1365,7 +1365,7 @@
         <v>39</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>2</v>
@@ -1533,7 +1533,7 @@
         <v>39</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>2</v>
@@ -1561,7 +1561,7 @@
         <v>39</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>2</v>
@@ -1757,7 +1757,7 @@
         <v>13</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>5</v>
@@ -1785,7 +1785,7 @@
         <v>13</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>6</v>
@@ -1813,7 +1813,7 @@
         <v>13</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>5</v>

--- a/Documentation/DocRenew_Jira_Task_Sheet.xlsx
+++ b/Documentation/DocRenew_Jira_Task_Sheet.xlsx
@@ -1841,7 +1841,7 @@
         <v>13</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>8</v>
@@ -1869,7 +1869,7 @@
         <v>13</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>3</v>

--- a/Documentation/DocRenew_Jira_Task_Sheet.xlsx
+++ b/Documentation/DocRenew_Jira_Task_Sheet.xlsx
@@ -2392,7 +2392,7 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H46" s="14" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H47" s="14" t="n">

--- a/Documentation/DocRenew_Jira_Task_Sheet.xlsx
+++ b/Documentation/DocRenew_Jira_Task_Sheet.xlsx
@@ -2476,7 +2476,7 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H48" s="14" t="n">

--- a/Documentation/DocRenew_Jira_Task_Sheet.xlsx
+++ b/Documentation/DocRenew_Jira_Task_Sheet.xlsx
@@ -2518,7 +2518,7 @@
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H49" s="14" t="n">

--- a/Documentation/DocRenew_Jira_Task_Sheet.xlsx
+++ b/Documentation/DocRenew_Jira_Task_Sheet.xlsx
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H50" s="14" t="n">
